--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -925,8 +925,8 @@
       <c r="M15" s="14">
         <v>300</v>
       </c>
-      <c r="N15" s="13" t="s">
-        <v>21</v>
+      <c r="N15" s="14">
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>-42.857142857142</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L16" s="14">
-        <v>-20</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M16" s="14">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.489361702127</v>
+        <v>-90.654205607476</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H17" s="14">
-        <v>9.090909090909</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="I17" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J17" s="15">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K17" s="14">
-        <v>6.25</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="L17" s="14">
-        <v>-10.526315789473</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="M17" s="14">
-        <v>88.888888888888</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N17" s="14">
-        <v>-41.379310344827</v>
+        <v>-42.424242424242</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
         <v>13</v>
       </c>
       <c r="H18" s="14">
-        <v>-61.538461538461</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K18" s="14">
-        <v>-53.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L18" s="14">
-        <v>-53.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="M18" s="14">
-        <v>-87.5</v>
+        <v>-85.964912280701</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.634615384615</v>
+        <v>-96.694214876033</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="14">
-        <v>-16.666666666666</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G19" s="15">
         <v>32</v>
       </c>
       <c r="H19" s="14">
-        <v>-18.75</v>
+        <v>-31.25</v>
       </c>
       <c r="I19" s="15">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J19" s="15">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K19" s="14">
-        <v>-10</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="L19" s="14">
-        <v>-43.75</v>
+        <v>-47.297297297297</v>
       </c>
       <c r="M19" s="14">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
       <c r="N19" s="14">
-        <v>-53.246753246753</v>
+        <v>-54.117647058823</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
+        <v>6</v>
+      </c>
+      <c r="D20" s="15">
         <v>5</v>
       </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
       <c r="E20" s="14">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F20" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>177.777777777778</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I20" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J20" s="15">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K20" s="14">
-        <v>146.153846153846</v>
+        <v>111.111111111111</v>
       </c>
       <c r="L20" s="14">
-        <v>68.421052631578</v>
+        <v>52</v>
       </c>
       <c r="M20" s="14">
-        <v>146.153846153846</v>
+        <v>111.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-84.158415841584</v>
+        <v>-83.898305084745</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.764705882352</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F21" s="17">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>4.054054054054</v>
+        <v>-10.843373493975</v>
       </c>
       <c r="I21" s="17">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J21" s="17">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="K21" s="18">
-        <v>5.050505050505</v>
+        <v>-5.6</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.388059701492</v>
+        <v>-24.840764331210</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.275862068965</v>
+        <v>-27.607361963190</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.006535947712</v>
+        <v>-83.28611898017</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
+        <v>1</v>
+      </c>
+      <c r="G22" s="15">
         <v>2</v>
       </c>
-      <c r="G22" s="15">
-        <v>3</v>
-      </c>
       <c r="H22" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>-79.545454545454</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="F24" s="15">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G24" s="15">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="H24" s="14">
-        <v>-48.484848484848</v>
+        <v>-57.272727272727</v>
       </c>
       <c r="I24" s="15">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="J24" s="15">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="K24" s="14">
-        <v>-43.801652892562</v>
+        <v>-46.710526315789</v>
       </c>
       <c r="L24" s="14">
-        <v>-35.238095238095</v>
+        <v>-36.220472440944</v>
       </c>
       <c r="M24" s="14">
-        <v>-40.869565217391</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E25" s="14">
-        <v>-57.142857142857</v>
+        <v>100</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-21.428571428571</v>
+        <v>-18.75</v>
       </c>
       <c r="I25" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J25" s="15">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K25" s="14">
-        <v>-26.315789473684</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L25" s="14">
-        <v>-44</v>
+        <v>-40</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H26" s="14">
-        <v>-23.076923076923</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="I26" s="15">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J26" s="15">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K26" s="14">
-        <v>-15.789473684210</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L26" s="14">
-        <v>-21.951219512195</v>
+        <v>-18.75</v>
       </c>
       <c r="M26" s="14">
-        <v>-25.581395348837</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
+      </c>
+      <c r="F28" s="15">
+        <v>7</v>
+      </c>
+      <c r="G28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>6</v>
-      </c>
-      <c r="G28" s="15">
-        <v>1</v>
-      </c>
       <c r="H28" s="14">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L28" s="14">
-        <v>-36.363636363636</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,32 +895,32 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G15" s="15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="14">
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>4</v>
       </c>
       <c r="J15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L15" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M15" s="14">
         <v>300</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="15">
         <v>2</v>
       </c>
-      <c r="D16" s="15">
-        <v>3</v>
-      </c>
       <c r="E16" s="14">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="15">
         <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>-41.176470588235</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="L16" s="14">
-        <v>-9.090909090909</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M16" s="14">
-        <v>-58.333333333333</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.654205607476</v>
+        <v>-92.125984251968</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,13 +975,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>3</v>
+      </c>
+      <c r="D17" s="15">
         <v>2</v>
       </c>
-      <c r="D17" s="15">
-        <v>5</v>
-      </c>
       <c r="E17" s="14">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
         <v>11</v>
@@ -993,63 +993,63 @@
         <v>-21.428571428571</v>
       </c>
       <c r="I17" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J17" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K17" s="14">
-        <v>-9.523809523809</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L17" s="14">
-        <v>-13.636363636363</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M17" s="14">
-        <v>72.727272727272</v>
+        <v>46.666666666666</v>
       </c>
       <c r="N17" s="14">
-        <v>-42.424242424242</v>
+        <v>-37.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="14">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H18" s="14">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
-        <v>-57.894736842105</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="L18" s="14">
-        <v>-55.555555555555</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="14">
-        <v>-85.964912280701</v>
+        <v>-85.245901639344</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.694214876033</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D19" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="14">
-        <v>-66.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="15">
         <v>22</v>
       </c>
       <c r="G19" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H19" s="14">
-        <v>-31.25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="15">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J19" s="15">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="K19" s="14">
-        <v>-20.408163265306</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L19" s="14">
-        <v>-47.297297297297</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M19" s="14">
-        <v>-25</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N19" s="14">
-        <v>-54.117647058823</v>
+        <v>-51.515151515151</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D20" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="F20" s="15">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G20" s="15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H20" s="14">
-        <v>85.714285714285</v>
+        <v>130</v>
       </c>
       <c r="I20" s="15">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="J20" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="14">
-        <v>111.111111111111</v>
+        <v>147.368421052632</v>
       </c>
       <c r="L20" s="14">
-        <v>52</v>
+        <v>74.074074074074</v>
       </c>
       <c r="M20" s="14">
-        <v>111.111111111111</v>
+        <v>135</v>
       </c>
       <c r="N20" s="14">
-        <v>-83.898305084745</v>
+        <v>-82.783882783882</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.153846153846</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.843373493975</v>
+        <v>-13.924050632911</v>
       </c>
       <c r="I21" s="17">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="J21" s="17">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.6</v>
+        <v>-0.709219858156</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.840764331210</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="M21" s="18">
-        <v>-27.607361963190</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.28611898017</v>
+        <v>-83.030303030303</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="15">
         <v>1</v>
       </c>
-      <c r="G22" s="15">
-        <v>2</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-50</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>2</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="15">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E24" s="14">
-        <v>-61.290322580645</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F24" s="15">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G24" s="15">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H24" s="14">
-        <v>-57.272727272727</v>
+        <v>-59.821428571428</v>
       </c>
       <c r="I24" s="15">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="J24" s="15">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="K24" s="14">
-        <v>-46.710526315789</v>
+        <v>-46.470588235294</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.220472440944</v>
+        <v>-36.805555555555</v>
       </c>
       <c r="M24" s="14">
-        <v>-37.209302325581</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
+        <v>2</v>
+      </c>
+      <c r="D25" s="15">
         <v>4</v>
       </c>
-      <c r="D25" s="15">
-        <v>2</v>
-      </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G25" s="15">
         <v>16</v>
       </c>
       <c r="H25" s="14">
-        <v>-18.75</v>
+        <v>-31.25</v>
       </c>
       <c r="I25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J25" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K25" s="14">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="L25" s="14">
-        <v>-40</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="15">
         <v>7</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F26" s="15">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H26" s="14">
-        <v>-27.586206896551</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I26" s="15">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J26" s="15">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K26" s="14">
-        <v>-13.333333333333</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="L26" s="14">
-        <v>-18.75</v>
+        <v>-7.272727272727</v>
       </c>
       <c r="M26" s="14">
-        <v>-20.408163265306</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G27" s="15">
+        <v>2</v>
+      </c>
+      <c r="H27" s="14">
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="14">
         <v>0</v>
       </c>
       <c r="F28" s="15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="15">
+        <v>4</v>
+      </c>
+      <c r="H28" s="14">
+        <v>25</v>
+      </c>
+      <c r="I28" s="15">
+        <v>9</v>
+      </c>
+      <c r="J28" s="15">
         <v>7</v>
       </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
-      <c r="H28" s="14">
-        <v>250</v>
-      </c>
-      <c r="I28" s="15">
-        <v>8</v>
-      </c>
-      <c r="J28" s="15">
-        <v>5</v>
-      </c>
       <c r="K28" s="14">
-        <v>60</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L28" s="14">
-        <v>-38.461538461538</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
-        <v>2</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -920,54 +920,54 @@
         <v>100</v>
       </c>
       <c r="L15" s="14">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M15" s="14">
         <v>300</v>
       </c>
       <c r="N15" s="14">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-14.285714285714</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="14">
-        <v>-47.368421052631</v>
+        <v>-45</v>
       </c>
       <c r="L16" s="14">
-        <v>-23.076923076923</v>
+        <v>-31.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-61.538461538461</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.125984251968</v>
+        <v>-92.086330935251</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
         <v>3</v>
       </c>
-      <c r="D17" s="15">
-        <v>2</v>
-      </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-21.428571428571</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I17" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J17" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K17" s="14">
-        <v>-4.347826086956</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L17" s="14">
-        <v>-15.384615384615</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M17" s="14">
-        <v>46.666666666666</v>
+        <v>41.176470588235</v>
       </c>
       <c r="N17" s="14">
-        <v>-37.142857142857</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>6</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>20</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" s="14">
-        <v>-64.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K18" s="14">
-        <v>-59.090909090909</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L18" s="14">
-        <v>-50</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M18" s="14">
-        <v>-85.245901639344</v>
+        <v>-76.190476190476</v>
       </c>
       <c r="N18" s="14">
-        <v>-96.875</v>
+        <v>-95.283018867924</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>6</v>
+      </c>
+      <c r="D19" s="15">
         <v>9</v>
       </c>
-      <c r="D19" s="15">
-        <v>7</v>
-      </c>
       <c r="E19" s="14">
-        <v>28.571428571428</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-33.333333333333</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I19" s="15">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="J19" s="15">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K19" s="14">
-        <v>-14.285714285714</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="L19" s="14">
-        <v>-42.857142857142</v>
+        <v>-46.534653465346</v>
       </c>
       <c r="M19" s="14">
-        <v>-15.789473684210</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="N19" s="14">
-        <v>-51.515151515151</v>
+        <v>-51.351351351351</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" s="14">
-        <v>800</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="15">
         <v>23</v>
       </c>
       <c r="G20" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H20" s="14">
-        <v>130</v>
+        <v>64.285714285714</v>
       </c>
       <c r="I20" s="15">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J20" s="15">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K20" s="14">
-        <v>147.368421052632</v>
+        <v>100</v>
       </c>
       <c r="L20" s="14">
-        <v>74.074074074074</v>
+        <v>72.413793103448</v>
       </c>
       <c r="M20" s="14">
-        <v>135</v>
+        <v>138.095238095238</v>
       </c>
       <c r="N20" s="14">
-        <v>-82.783882783882</v>
+        <v>-84.375</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F21" s="17">
         <v>68</v>
       </c>
       <c r="G21" s="17">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.924050632911</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="I21" s="17">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="J21" s="17">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.709219858156</v>
+        <v>-4.242424242424</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.454545454545</v>
+        <v>-23.671497584541</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.222222222222</v>
+        <v>-18.134715025906</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.030303030303</v>
+        <v>-83.047210300429</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="14">
-        <v>-44.444444444444</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="15">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G24" s="15">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-59.821428571428</v>
+        <v>-59.292035398230</v>
       </c>
       <c r="I24" s="15">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J24" s="15">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="K24" s="14">
-        <v>-46.470588235294</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="L24" s="14">
-        <v>-36.805555555555</v>
+        <v>-35.975609756097</v>
       </c>
       <c r="M24" s="14">
-        <v>-36.363636363636</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D25" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E25" s="14">
-        <v>-50</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F25" s="15">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G25" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H25" s="14">
-        <v>-31.25</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="15">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J25" s="15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="K25" s="14">
-        <v>-20</v>
+        <v>-12.5</v>
       </c>
       <c r="L25" s="14">
-        <v>-41.176470588235</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="14">
-        <v>71.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G26" s="15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H26" s="14">
-        <v>-3.333333333333</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="I26" s="15">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J26" s="15">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K26" s="14">
-        <v>-1.923076923076</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.272727272727</v>
+        <v>-25.352112676056</v>
       </c>
       <c r="M26" s="14">
-        <v>-10.526315789473</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
         <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="L28" s="14">
-        <v>-30.769230769230</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,8 +869,8 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -878,22 +878,22 @@
       <c r="K14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="14">
-        <v>-100</v>
+      <c r="L14" s="15">
+        <v>-50</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
-        <v>-100</v>
+      <c r="N14" s="15">
+        <v>-50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,237 +901,237 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
         <v>0</v>
       </c>
-      <c r="I15" s="15">
-        <v>4</v>
-      </c>
-      <c r="J15" s="15">
+      <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="K15" s="14">
-        <v>100</v>
-      </c>
-      <c r="L15" s="14">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="M15" s="14">
-        <v>300</v>
-      </c>
-      <c r="N15" s="14">
-        <v>100</v>
+      <c r="K15" s="15">
+        <v>150</v>
+      </c>
+      <c r="L15" s="15">
+        <v>-28.571428571428</v>
+      </c>
+      <c r="M15" s="15">
+        <v>400</v>
+      </c>
+      <c r="N15" s="15">
+        <v>66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <v>5</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <v>8</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="15">
         <v>-37.5</v>
       </c>
-      <c r="I16" s="15">
-        <v>11</v>
-      </c>
-      <c r="J16" s="15">
-        <v>20</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-45</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-31.25</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-57.692307692307</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-92.086330935251</v>
+      <c r="I16" s="14">
+        <v>13</v>
+      </c>
+      <c r="J16" s="14">
+        <v>22</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-40.909090909090</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-27.777777777777</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-58.064516129032</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-91.095890410958</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
-        <v>3</v>
-      </c>
-      <c r="E17" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F17" s="15">
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>4</v>
+      </c>
+      <c r="E17" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="14">
         <v>8</v>
       </c>
-      <c r="G17" s="15">
-        <v>13</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-38.461538461538</v>
-      </c>
-      <c r="I17" s="15">
-        <v>24</v>
-      </c>
-      <c r="J17" s="15">
+      <c r="G17" s="14">
+        <v>14</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="I17" s="14">
         <v>26</v>
       </c>
-      <c r="K17" s="14">
-        <v>-7.692307692307</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-27.272727272727</v>
-      </c>
-      <c r="M17" s="14">
-        <v>41.176470588235</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-40</v>
+      <c r="J17" s="14">
+        <v>30</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-13.333333333333</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-35</v>
+      </c>
+      <c r="M17" s="15">
+        <v>36.842105263157</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-44.680851063829</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>6</v>
-      </c>
-      <c r="D18" s="15">
-        <v>5</v>
-      </c>
-      <c r="E18" s="14">
-        <v>20</v>
-      </c>
-      <c r="F18" s="15">
-        <v>8</v>
-      </c>
-      <c r="G18" s="15">
-        <v>16</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I18" s="15">
-        <v>15</v>
-      </c>
-      <c r="J18" s="15">
-        <v>27</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-44.444444444444</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-21.052631578947</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-76.190476190476</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-95.283018867924</v>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>50</v>
+      </c>
+      <c r="F18" s="14">
+        <v>11</v>
+      </c>
+      <c r="G18" s="14">
+        <v>14</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-21.428571428571</v>
+      </c>
+      <c r="I18" s="14">
+        <v>18</v>
+      </c>
+      <c r="J18" s="14">
+        <v>29</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-37.931034482758</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-5.263157894736</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-74.285714285714</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-94.842406876790</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>6</v>
-      </c>
-      <c r="D19" s="15">
-        <v>9</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F19" s="15">
-        <v>23</v>
-      </c>
-      <c r="G19" s="15">
-        <v>31</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-25.806451612903</v>
-      </c>
-      <c r="I19" s="15">
-        <v>54</v>
-      </c>
-      <c r="J19" s="15">
-        <v>65</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-16.923076923076</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-46.534653465346</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-16.923076923076</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-51.351351351351</v>
+      <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
+        <v>7</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>25</v>
+      </c>
+      <c r="G19" s="14">
+        <v>32</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-21.875</v>
+      </c>
+      <c r="I19" s="14">
+        <v>61</v>
+      </c>
+      <c r="J19" s="14">
+        <v>72</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-15.277777777777</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-42.452830188679</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-8.955223880597</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-49.166666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="15">
-        <v>6</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-50</v>
-      </c>
-      <c r="F20" s="15">
-        <v>23</v>
-      </c>
-      <c r="G20" s="15">
-        <v>14</v>
-      </c>
-      <c r="H20" s="14">
-        <v>64.285714285714</v>
-      </c>
-      <c r="I20" s="15">
-        <v>50</v>
-      </c>
-      <c r="J20" s="15">
-        <v>25</v>
-      </c>
-      <c r="K20" s="14">
-        <v>100</v>
-      </c>
-      <c r="L20" s="14">
-        <v>72.413793103448</v>
-      </c>
-      <c r="M20" s="14">
-        <v>138.095238095238</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-84.375</v>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>21</v>
+      </c>
+      <c r="G20" s="14">
+        <v>15</v>
+      </c>
+      <c r="H20" s="15">
+        <v>40</v>
+      </c>
+      <c r="I20" s="14">
+        <v>53</v>
+      </c>
+      <c r="J20" s="14">
+        <v>28</v>
+      </c>
+      <c r="K20" s="15">
+        <v>89.285714285714</v>
+      </c>
+      <c r="L20" s="15">
+        <v>60.606060606060</v>
+      </c>
+      <c r="M20" s="15">
+        <v>103.846153846154</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-85.154061624649</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.166666666666</v>
+        <v>5.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.072289156626</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.242424242424</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.671497584541</v>
+        <v>-21.333333333333</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.134715025906</v>
+        <v>-17.289719626168</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.047210300429</v>
+        <v>-82.71484375</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,34 +1182,34 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="15">
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I22" s="14">
         <v>2</v>
       </c>
-      <c r="J22" s="15">
-        <v>3</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L22" s="14">
+      <c r="J22" s="14">
+        <v>4</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L22" s="15">
         <v>0</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="15">
         <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>14</v>
-      </c>
-      <c r="D24" s="15">
-        <v>20</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-30</v>
-      </c>
-      <c r="F24" s="15">
-        <v>46</v>
-      </c>
-      <c r="G24" s="15">
-        <v>113</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-59.292035398230</v>
-      </c>
-      <c r="I24" s="15">
-        <v>105</v>
-      </c>
-      <c r="J24" s="15">
-        <v>190</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-44.736842105263</v>
-      </c>
-      <c r="L24" s="14">
-        <v>-35.975609756097</v>
-      </c>
-      <c r="M24" s="14">
+      <c r="C24" s="14">
+        <v>15</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-25</v>
+      </c>
+      <c r="F24" s="14">
+        <v>51</v>
+      </c>
+      <c r="G24" s="14">
+        <v>89</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-42.696629213483</v>
+      </c>
+      <c r="I24" s="14">
+        <v>120</v>
+      </c>
+      <c r="J24" s="14">
+        <v>210</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-42.857142857142</v>
+      </c>
+      <c r="L24" s="15">
         <v>-31.818181818181</v>
+      </c>
+      <c r="M24" s="15">
+        <v>-27.272727272727</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>8</v>
-      </c>
-      <c r="D25" s="15">
-        <v>7</v>
-      </c>
-      <c r="E25" s="14">
-        <v>14.285714285714</v>
-      </c>
-      <c r="F25" s="15">
-        <v>17</v>
-      </c>
-      <c r="G25" s="15">
-        <v>20</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-15</v>
-      </c>
-      <c r="I25" s="15">
-        <v>28</v>
-      </c>
-      <c r="J25" s="15">
-        <v>32</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-33.333333333333</v>
+      <c r="C25" s="14">
+        <v>5</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F25" s="14">
+        <v>19</v>
+      </c>
+      <c r="G25" s="14">
+        <v>16</v>
+      </c>
+      <c r="H25" s="15">
+        <v>18.75</v>
+      </c>
+      <c r="I25" s="14">
+        <v>33</v>
+      </c>
+      <c r="J25" s="14">
+        <v>35</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-5.714285714285</v>
+      </c>
+      <c r="L25" s="15">
+        <v>-25</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>3</v>
-      </c>
-      <c r="D26" s="15">
-        <v>9</v>
-      </c>
-      <c r="E26" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F26" s="15">
-        <v>27</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C26" s="14">
+        <v>7</v>
+      </c>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>29</v>
+      </c>
+      <c r="G26" s="14">
         <v>31</v>
       </c>
-      <c r="H26" s="14">
-        <v>-12.903225806451</v>
-      </c>
-      <c r="I26" s="15">
-        <v>53</v>
-      </c>
-      <c r="J26" s="15">
-        <v>61</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-13.114754098360</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-25.352112676056</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-13.114754098360</v>
+      <c r="H26" s="15">
+        <v>-6.451612903225</v>
+      </c>
+      <c r="I26" s="14">
+        <v>60</v>
+      </c>
+      <c r="J26" s="14">
+        <v>69</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-13.043478260869</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-25</v>
+      </c>
+      <c r="M26" s="15">
+        <v>-10.447761194029</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,26 +1393,26 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
-      </c>
-      <c r="G27" s="15">
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>-50</v>
       </c>
-      <c r="I27" s="15">
-        <v>5</v>
-      </c>
-      <c r="J27" s="15">
+      <c r="I27" s="14">
+        <v>6</v>
+      </c>
+      <c r="J27" s="14">
         <v>3</v>
       </c>
-      <c r="K27" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="L27" s="14">
-        <v>-50</v>
+      <c r="K27" s="15">
+        <v>100</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
-      <c r="G28" s="15">
-        <v>4</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-25</v>
-      </c>
-      <c r="I28" s="15">
-        <v>8</v>
-      </c>
-      <c r="J28" s="15">
-        <v>8</v>
-      </c>
-      <c r="K28" s="14">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
         <v>0</v>
       </c>
-      <c r="L28" s="14">
-        <v>-52.941176470588</v>
+      <c r="F28" s="14">
+        <v>2</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-60</v>
+      </c>
+      <c r="I28" s="14">
+        <v>9</v>
+      </c>
+      <c r="J28" s="14">
+        <v>9</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-52.631578947368</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1496,19 +1496,19 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N29" s="14">
-        <v>-100</v>
+      <c r="M29" s="15">
+        <v>0</v>
+      </c>
+      <c r="N29" s="15">
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1537,19 +1537,19 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="14">
-        <v>-100</v>
-      </c>
-      <c r="N30" s="14">
-        <v>-100</v>
+      <c r="M30" s="15">
+        <v>0</v>
+      </c>
+      <c r="N30" s="15">
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="15">
-        <v>4</v>
+      <c r="I31" s="14">
+        <v>5</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="14">
-        <v>300</v>
+      <c r="L31" s="15">
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>9</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>10</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>4</v>
       </c>
-      <c r="I39" s="15">
-        <v>1</v>
-      </c>
-      <c r="J39" s="15">
-        <v>1</v>
-      </c>
-      <c r="K39" s="14">
+      <c r="I39" s="14">
+        <v>1</v>
+      </c>
+      <c r="J39" s="14">
+        <v>1</v>
+      </c>
+      <c r="K39" s="15">
         <v>0</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-75</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-90</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-88.888888888888</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>15</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>19</v>
       </c>
-      <c r="G40" s="15">
-        <v>20</v>
-      </c>
-      <c r="I40" s="15">
+      <c r="G40" s="14">
+        <v>20</v>
+      </c>
+      <c r="I40" s="14">
         <v>17</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>18</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>5.882352941176</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>-10</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-5.263157894736</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>20</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>835</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>747</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>406</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>282</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>102</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-63.829787234042</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-74.876847290640</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-86.345381526104</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-87.784431137724</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>286</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>314</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>215</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>212</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>224</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>5.660377358490</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>4.186046511627</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-28.662420382165</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-21.678321678321</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>2676</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>1692</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>795</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>552</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>115</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-79.166666666666</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-85.534591194968</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-93.203309692671</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-95.702541106128</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>831</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>661</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>416</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>353</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>462</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>30.878186968838</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>11.057692307692</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-30.105900151285</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-44.404332129963</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>3275</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>1821</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>805</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>445</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>221</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-50.337078651685</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-72.546583850931</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-87.863811092806</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-93.251908396946</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L15" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
+        <v>200</v>
+      </c>
+      <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>5</v>
-      </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-37.5</v>
-      </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.909090909090</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.777777777777</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.064516129032</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.095890410958</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>-42.857142857142</v>
+        <v>9.090909090909</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-35</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M17" s="15">
-        <v>36.842105263157</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.680851063829</v>
+        <v>-40.740740740740</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F18" s="14">
+        <v>13</v>
+      </c>
+      <c r="G18" s="14">
         <v>11</v>
       </c>
-      <c r="G18" s="14">
-        <v>14</v>
-      </c>
       <c r="H18" s="15">
-        <v>-21.428571428571</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.931034482758</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.263157894736</v>
+        <v>10</v>
       </c>
       <c r="M18" s="15">
-        <v>-74.285714285714</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.842406876790</v>
+        <v>-94.133333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-21.875</v>
+        <v>-2.941176470588</v>
       </c>
       <c r="I19" s="14">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.277777777777</v>
+        <v>-13.253012048192</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.452830188679</v>
+        <v>-40.983606557377</v>
       </c>
       <c r="M19" s="15">
-        <v>-8.955223880597</v>
+        <v>-2.702702702702</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.166666666666</v>
+        <v>-43.75</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
         <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K20" s="15">
-        <v>89.285714285714</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>60.606060606060</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M20" s="15">
-        <v>103.846153846154</v>
+        <v>103.703703703704</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.154061624649</v>
+        <v>-85.824742268041</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>5.555555555555</v>
+        <v>40</v>
       </c>
       <c r="F21" s="17">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.285714285714</v>
+        <v>8.974358974358</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="J21" s="17">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.278688524590</v>
+        <v>0.492610837438</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.333333333333</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.289719626168</v>
+        <v>-13.924050632911</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.71484375</v>
+        <v>-81.621621621621</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,10 +1201,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G24" s="14">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>-42.696629213483</v>
+        <v>-32.926829268292</v>
       </c>
       <c r="I24" s="14">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="J24" s="14">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="K24" s="15">
-        <v>-42.857142857142</v>
+        <v>-41.880341880341</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.818181818181</v>
+        <v>-32</v>
       </c>
       <c r="M24" s="15">
-        <v>-27.272727272727</v>
+        <v>-22.285714285714</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H25" s="15">
-        <v>18.75</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.714285714285</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="L25" s="15">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>-60</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-6.451612903225</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J26" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.043478260869</v>
+        <v>-20.253164556962</v>
       </c>
       <c r="L26" s="15">
-        <v>-25</v>
+        <v>-29.213483146067</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.447761194029</v>
+        <v>-23.170731707317</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>2</v>
@@ -1444,16 +1444,16 @@
         <v>-60</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-52.631578947368</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -885,15 +885,15 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="15">
-        <v>200</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
         <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.434782608695</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.111111111111</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M16" s="15">
-        <v>-55.555555555555</v>
+        <v>-56.097560975609</v>
       </c>
       <c r="N16" s="15">
-        <v>-90</v>
+        <v>-89.944134078212</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
+        <v>13</v>
+      </c>
+      <c r="G17" s="14">
         <v>12</v>
       </c>
-      <c r="G17" s="14">
-        <v>11</v>
-      </c>
       <c r="H17" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>2.857142857142</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.809523809523</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="M17" s="15">
-        <v>45.454545454545</v>
+        <v>16.129032258064</v>
       </c>
       <c r="N17" s="15">
-        <v>-40.740740740740</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>300</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
         <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.666666666666</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="L18" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>-71.428571428571</v>
+        <v>-73.563218390804</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.133333333333</v>
+        <v>-94.221105527638</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14">
         <v>10</v>
       </c>
-      <c r="D19" s="14">
-        <v>11</v>
-      </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>-60</v>
       </c>
       <c r="F19" s="14">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.941176470588</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="I19" s="14">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J19" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.253012048192</v>
+        <v>-18.279569892473</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.983606557377</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M19" s="15">
-        <v>-2.702702702702</v>
+        <v>1.333333333333</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.75</v>
+        <v>-48.299319727891</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I20" s="14">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J20" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>66.666666666666</v>
+        <v>55.263157894736</v>
       </c>
       <c r="L20" s="15">
-        <v>57.142857142857</v>
+        <v>59.459459459459</v>
       </c>
       <c r="M20" s="15">
-        <v>103.703703703704</v>
+        <v>78.787878787878</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.824742268041</v>
+        <v>-86.247086247086</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="G21" s="17">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H21" s="18">
-        <v>8.974358974358</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="I21" s="17">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="K21" s="18">
-        <v>0.492610837438</v>
+        <v>-2.232142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.073170731707</v>
+        <v>-17.045454545454</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.924050632911</v>
+        <v>-18.283582089552</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.621621621621</v>
+        <v>-82.034454470877</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,10 +1201,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-33.333333333333</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F24" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.926829268292</v>
+        <v>-30.864197530864</v>
       </c>
       <c r="I24" s="14">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="J24" s="14">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="K24" s="15">
-        <v>-41.880341880341</v>
+        <v>-41.434262948207</v>
       </c>
       <c r="L24" s="15">
-        <v>-32</v>
+        <v>-31.627906976744</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.285714285714</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>3</v>
       </c>
-      <c r="D25" s="14">
-        <v>8</v>
-      </c>
       <c r="E25" s="15">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G25" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.181818181818</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I25" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.279069767441</v>
+        <v>-19.565217391304</v>
       </c>
       <c r="L25" s="15">
-        <v>-28</v>
+        <v>-31.481481481481</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>-60</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-26.470588235294</v>
+        <v>-34.375</v>
       </c>
       <c r="I26" s="14">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="J26" s="14">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.253164556962</v>
+        <v>-15.476190476190</v>
       </c>
       <c r="L26" s="15">
-        <v>-29.213483146067</v>
+        <v>-27.551020408163</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.170731707317</v>
+        <v>-21.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>0</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>8</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-60</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-57.894736842105</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>2</v>
+      </c>
+      <c r="K31" s="15">
+        <v>150</v>
       </c>
       <c r="L31" s="15">
         <v>66.666666666666</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -885,15 +885,15 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="L15" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="N15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.739130434782</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L16" s="15">
-        <v>-5.263157894736</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.097560975609</v>
+        <v>-56.25</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.944134078212</v>
+        <v>-89.0625</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
+        <v>16</v>
+      </c>
+      <c r="G17" s="14">
         <v>13</v>
       </c>
-      <c r="G17" s="14">
-        <v>12</v>
-      </c>
       <c r="H17" s="15">
-        <v>8.333333333333</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I17" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>2.857142857142</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.279069767441</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M17" s="15">
-        <v>16.129032258064</v>
+        <v>25</v>
       </c>
       <c r="N17" s="15">
-        <v>-40</v>
+        <v>-36.507936507936</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>27.272727272727</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.303030303030</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-73.563218390804</v>
+        <v>-67.777777777777</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.221105527638</v>
+        <v>-93.255813953488</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-60</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.324324324324</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="I19" s="14">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J19" s="14">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.279569892473</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.857142857142</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M19" s="15">
-        <v>1.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.299319727891</v>
+        <v>-42.675159235668</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H20" s="15">
-        <v>-31.578947368421</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>55.263157894736</v>
+        <v>27.659574468085</v>
       </c>
       <c r="L20" s="15">
-        <v>59.459459459459</v>
+        <v>50</v>
       </c>
       <c r="M20" s="15">
-        <v>78.787878787878</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.247086247086</v>
+        <v>-86.984815618221</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>-33.333333333333</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="F21" s="17">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G21" s="17">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.819277108433</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I21" s="17">
-        <v>219</v>
+        <v>248</v>
       </c>
       <c r="J21" s="17">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.232142857142</v>
+        <v>-3.875968992248</v>
       </c>
       <c r="L21" s="18">
-        <v>-17.045454545454</v>
+        <v>-13.286713286713</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.283582089552</v>
+        <v>-16.498316498316</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.034454470877</v>
+        <v>-81.068702290076</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="14">
         <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-35.294117647058</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F24" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G24" s="14">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.864197530864</v>
+        <v>-28.378378378378</v>
       </c>
       <c r="I24" s="14">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J24" s="14">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="K24" s="15">
-        <v>-41.434262948207</v>
+        <v>-40.151515151515</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.627906976744</v>
+        <v>-33.891213389121</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.222222222222</v>
+        <v>-22.167487684729</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
+        <v>12</v>
+      </c>
+      <c r="G25" s="14">
         <v>17</v>
       </c>
-      <c r="G25" s="14">
-        <v>21</v>
-      </c>
       <c r="H25" s="15">
-        <v>-19.047619047619</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K25" s="15">
-        <v>-19.565217391304</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.481481481481</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.375</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.476190476190</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="L26" s="15">
-        <v>-27.551020408163</v>
+        <v>-26.923076923076</v>
       </c>
       <c r="M26" s="15">
-        <v>-21.111111111111</v>
+        <v>-24.752475247524</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>166.666666666667</v>
+        <v>233.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>4</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>9.090909090909</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1552,31 +1552,31 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1634,8 +1634,8 @@
       <c r="K33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="13" t="s">
-        <v>21</v>
+      <c r="L33" s="15">
+        <v>-50</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -885,39 +885,39 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>80</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-19.230769230769</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.545454545454</v>
+        <v>-8</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.25</v>
+        <v>-54</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.0625</v>
+        <v>-88.834951456310</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>23.076923076923</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="K17" s="15">
-        <v>2.564102564102</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.893617021276</v>
+        <v>-8</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>31.428571428571</v>
       </c>
       <c r="N17" s="15">
-        <v>-36.507936507936</v>
+        <v>-29.230769230769</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>6</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H18" s="15">
-        <v>55.555555555555</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.444444444444</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.333333333333</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M18" s="15">
-        <v>-67.777777777777</v>
+        <v>-69.565217391304</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.255813953488</v>
+        <v>-94.042553191489</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-6.666666666666</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G19" s="14">
         <v>43</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.604651162790</v>
+        <v>-30.232558139534</v>
       </c>
       <c r="I19" s="14">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J19" s="14">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.782608695652</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="M19" s="15">
-        <v>0</v>
+        <v>-5.154639175257</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.675159235668</v>
+        <v>-45.238095238095</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-88.888888888888</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-32</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K20" s="15">
-        <v>27.659574468085</v>
+        <v>28.301886792452</v>
       </c>
       <c r="L20" s="15">
-        <v>50</v>
+        <v>54.545454545454</v>
       </c>
       <c r="M20" s="15">
-        <v>71.428571428571</v>
+        <v>83.783783783783</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.984815618221</v>
+        <v>-86.534653465346</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.647058823529</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.225806451612</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I21" s="17">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="J21" s="17">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.875968992248</v>
+        <v>-6.028368794326</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.286713286713</v>
+        <v>-15.335463258785</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.498316498316</v>
+        <v>-15.335463258785</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.068702290076</v>
+        <v>-81.364275668073</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1210,7 +1210,7 @@
         <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-15.384615384615</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="F24" s="14">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.378378378378</v>
+        <v>-42.465753424657</v>
       </c>
       <c r="I24" s="14">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="K24" s="15">
-        <v>-40.151515151515</v>
+        <v>-42.756183745583</v>
       </c>
       <c r="L24" s="15">
-        <v>-33.891213389121</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="M24" s="15">
-        <v>-22.167487684729</v>
+        <v>-25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-29.411764705882</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J25" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.367346938775</v>
+        <v>-18</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.333333333333</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>-20.689655172413</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.555555555555</v>
+        <v>-18</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.923076923076</v>
+        <v>-24.770642201834</v>
       </c>
       <c r="M26" s="15">
-        <v>-24.752475247524</v>
+        <v>-25.454545454545</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>233.333333333333</v>
+        <v>150</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-50</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-13.333333333333</v>
+        <v>6.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-38.095238095238</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>100</v>
       </c>
       <c r="N29" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,25 +1558,25 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I31" s="14">
         <v>6</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -911,22 +911,22 @@
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M15" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>4</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>-14.814814814814</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="L16" s="15">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-54</v>
+        <v>-46</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.834951456310</v>
+        <v>-87.142857142857</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>25</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>17.647058823529</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.127659574468</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="M17" s="15">
-        <v>31.428571428571</v>
+        <v>30.769230769230</v>
       </c>
       <c r="N17" s="15">
-        <v>-29.230769230769</v>
+        <v>-26.086956521739</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J18" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.324324324324</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.151515151515</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="M18" s="15">
-        <v>-69.565217391304</v>
+        <v>-71.028037383177</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.042553191489</v>
+        <v>-93.686354378818</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-71.428571428571</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="14">
         <v>30</v>
@@ -1075,22 +1075,22 @@
         <v>-30.232558139534</v>
       </c>
       <c r="I19" s="14">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>-20</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="L19" s="15">
-        <v>-39.473684210526</v>
+        <v>-37.804878048780</v>
       </c>
       <c r="M19" s="15">
-        <v>-5.154639175257</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.238095238095</v>
+        <v>-43.333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H20" s="15">
-        <v>-32</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I20" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J20" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>28.301886792452</v>
+        <v>26.785714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>54.545454545454</v>
+        <v>51.063829787234</v>
       </c>
       <c r="M20" s="15">
-        <v>83.783783783783</v>
+        <v>65.116279069767</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.534653465346</v>
+        <v>-86.827458256029</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-29.166666666666</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G21" s="17">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.111111111111</v>
+        <v>-14.851485148514</v>
       </c>
       <c r="I21" s="17">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="J21" s="17">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.028368794326</v>
+        <v>-4.276315789473</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.335463258785</v>
+        <v>-15.652173913043</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.335463258785</v>
+        <v>-15.895953757225</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.364275668073</v>
+        <v>-80.561122244489</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>-78.947368421052</v>
+        <v>-74.074074074074</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G24" s="14">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>-42.465753424657</v>
+        <v>-56.578947368421</v>
       </c>
       <c r="I24" s="14">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J24" s="14">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="K24" s="15">
-        <v>-42.756183745583</v>
+        <v>-45.483870967741</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.209302325581</v>
+        <v>-39.857651245551</v>
       </c>
       <c r="M24" s="15">
-        <v>-25</v>
+        <v>-25.550660792951</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-87.5</v>
       </c>
       <c r="F25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
         <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="I25" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J25" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-18</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="L25" s="15">
-        <v>-32.786885245901</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>-22.580645161290</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J26" s="14">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="K26" s="15">
-        <v>-18</v>
+        <v>-20.183486238532</v>
       </c>
       <c r="L26" s="15">
-        <v>-24.770642201834</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="M26" s="15">
-        <v>-25.454545454545</v>
+        <v>-25</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="L27" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I28" s="14">
+        <v>20</v>
+      </c>
+      <c r="J28" s="14">
         <v>17</v>
       </c>
-      <c r="J28" s="14">
-        <v>16</v>
-      </c>
       <c r="K28" s="15">
-        <v>6.25</v>
+        <v>17.647058823529</v>
       </c>
       <c r="L28" s="15">
-        <v>-22.727272727272</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,25 +1558,25 @@
         <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H31" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L31" s="15">
-        <v>50</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="14">
+      <c r="D33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="E33" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>-50</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-6.896551724137</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-46</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.142857142857</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I17" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L17" s="15">
-        <v>-15</v>
+        <v>-16.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>30.769230769230</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.086956521739</v>
+        <v>-28.947368421052</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-20.512820512820</v>
+        <v>-15</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.421052631578</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="15">
-        <v>-71.028037383177</v>
+        <v>-70.434782608695</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.686354378818</v>
+        <v>-93.584905660377</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H19" s="15">
-        <v>-30.232558139534</v>
+        <v>-10</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J19" s="14">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K19" s="15">
-        <v>-19.047619047619</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.804878048780</v>
+        <v>-36</v>
       </c>
       <c r="M19" s="15">
-        <v>-2.857142857142</v>
+        <v>-2.608695652173</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.333333333333</v>
+        <v>-43.147208121827</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G20" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-30.434782608695</v>
+        <v>-32.142857142857</v>
       </c>
       <c r="I20" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K20" s="15">
-        <v>26.785714285714</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L20" s="15">
-        <v>51.063829787234</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M20" s="15">
-        <v>65.116279069767</v>
+        <v>73.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.827458256029</v>
+        <v>-86.757215619694</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>18.181818181818</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="F21" s="17">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.851485148514</v>
+        <v>-11.926605504587</v>
       </c>
       <c r="I21" s="17">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="J21" s="17">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.276315789473</v>
+        <v>-4.804804804804</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.652173913043</v>
+        <v>-14.092140921409</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.895953757225</v>
+        <v>-14.092140921409</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.561122244489</v>
+        <v>-80.492307692307</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
@@ -1207,7 +1207,7 @@
         <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-74.074074074074</v>
+        <v>109.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H24" s="15">
-        <v>-56.578947368421</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I24" s="14">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="J24" s="14">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="K24" s="15">
-        <v>-45.483870967741</v>
+        <v>-40.186915887850</v>
       </c>
       <c r="L24" s="15">
-        <v>-39.857651245551</v>
+        <v>-37.049180327868</v>
       </c>
       <c r="M24" s="15">
-        <v>-25.550660792951</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-87.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="14">
         <v>15</v>
       </c>
       <c r="H25" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.586206896551</v>
+        <v>-27.868852459016</v>
       </c>
       <c r="L25" s="15">
-        <v>-36.363636363636</v>
+        <v>-38.028169014084</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F26" s="14">
         <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H26" s="15">
-        <v>-16.666666666666</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="I26" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="J26" s="14">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>-20.183486238532</v>
+        <v>-22.314049586776</v>
       </c>
       <c r="L26" s="15">
-        <v>-25.641025641025</v>
+        <v>-26.5625</v>
       </c>
       <c r="M26" s="15">
-        <v>-25</v>
+        <v>-23.577235772357</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>85.714285714285</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>17.647058823529</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.090909090909</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
+        <v>2</v>
+      </c>
+      <c r="G31" s="14">
         <v>3</v>
       </c>
-      <c r="G31" s="14">
-        <v>5</v>
-      </c>
       <c r="H31" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="14">
         <v>7</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>8</v>
@@ -926,7 +926,7 @@
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>166.666666666667</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.764705882352</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>7.142857142857</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.396226415094</v>
+        <v>-43.859649122807</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.666666666666</v>
+        <v>-86.721991701244</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
         <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-22.727272727272</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.263157894736</v>
+        <v>-3.174603174603</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.923076923076</v>
+        <v>-19.736842105263</v>
       </c>
       <c r="M17" s="15">
-        <v>38.461538461538</v>
+        <v>48.780487804878</v>
       </c>
       <c r="N17" s="15">
-        <v>-28.947368421052</v>
+        <v>-32.967032967033</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>57.142857142857</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-15</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.526315789473</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.434782608695</v>
+        <v>-70.247933884297</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.584905660377</v>
+        <v>-93.466424682395</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="15">
-        <v>-10</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="I19" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J19" s="14">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="K19" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.006802721088</v>
       </c>
       <c r="L19" s="15">
-        <v>-36</v>
+        <v>-34.759358288770</v>
       </c>
       <c r="M19" s="15">
-        <v>-2.608695652173</v>
+        <v>0.826446280991</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.147208121827</v>
+        <v>-42.723004694835</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-30</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H20" s="15">
-        <v>-32.142857142857</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J20" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>18.181818181818</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>44.444444444444</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>73.333333333333</v>
+        <v>63.265306122449</v>
       </c>
       <c r="N20" s="15">
-        <v>-86.757215619694</v>
+        <v>-87.301587301587</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.344827586206</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.926605504587</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="J21" s="17">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="K21" s="18">
-        <v>-4.804804804804</v>
+        <v>-6.336088154269</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.092140921409</v>
+        <v>-14.357682619647</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.092140921409</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.492307692307</v>
+        <v>-80.414746543778</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>3</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>109.090909090909</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G24" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>-35.714285714285</v>
+        <v>-32.911392405063</v>
       </c>
       <c r="I24" s="14">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="J24" s="14">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="K24" s="15">
-        <v>-40.186915887850</v>
+        <v>-38.483965014577</v>
       </c>
       <c r="L24" s="15">
-        <v>-37.049180327868</v>
+        <v>-34.267912772585</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.951219512195</v>
+        <v>-19.465648854961</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-53.333333333333</v>
+        <v>-43.75</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.868852459016</v>
+        <v>-26.153846153846</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.028169014084</v>
+        <v>-36</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>-41.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H26" s="15">
-        <v>-32.432432432432</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.314049586776</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="L26" s="15">
-        <v>-26.5625</v>
+        <v>-25.373134328358</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.577235772357</v>
+        <v>-23.664122137404</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
@@ -1438,22 +1438,22 @@
         <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>42.857142857142</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>16.666666666666</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>-4.545454545454</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
+        <v>4</v>
+      </c>
+      <c r="G31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="14">
-        <v>3</v>
-      </c>
       <c r="H31" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J31" s="14">
         <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L31" s="15">
-        <v>16.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -911,22 +911,22 @@
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>166.666666666667</v>
+        <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="N15" s="15">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>11</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="I16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-8.571428571428</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L16" s="15">
-        <v>3.225806451612</v>
+        <v>-7.894736842105</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.859649122807</v>
+        <v>-40.677966101694</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.721991701244</v>
+        <v>-86.220472440944</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>16.666666666666</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
-        <v>-20.833333333333</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.174603174603</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-19.736842105263</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="M17" s="15">
-        <v>48.780487804878</v>
+        <v>61.904761904761</v>
       </c>
       <c r="N17" s="15">
-        <v>-32.967032967033</v>
+        <v>-32</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>14.285714285714</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
         <v>43</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.279069767441</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.263157894736</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.247933884297</v>
+        <v>-70.229007633587</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.466424682395</v>
+        <v>-93.298969072165</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.948717948717</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="I19" s="14">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J19" s="14">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.006802721088</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L19" s="15">
-        <v>-34.759358288770</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>0.826446280991</v>
+        <v>1.538461538461</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.723004694835</v>
+        <v>-42.608695652173</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-62.5</v>
       </c>
       <c r="F20" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="14">
+        <v>83</v>
+      </c>
+      <c r="J20" s="14">
         <v>80</v>
       </c>
-      <c r="J20" s="14">
-        <v>72</v>
-      </c>
       <c r="K20" s="15">
-        <v>11.111111111111</v>
+        <v>3.75</v>
       </c>
       <c r="L20" s="15">
-        <v>42.857142857142</v>
+        <v>45.614035087719</v>
       </c>
       <c r="M20" s="15">
-        <v>63.265306122449</v>
+        <v>66</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.301587301587</v>
+        <v>-87.556221889055</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.333333333333</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="I21" s="17">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="J21" s="17">
-        <v>363</v>
+        <v>391</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.336088154269</v>
+        <v>-6.649616368286</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.357682619647</v>
+        <v>-13.915094339622</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.043478260869</v>
+        <v>-11.835748792270</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.414746543778</v>
+        <v>-80.195333695062</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-62.5</v>
+        <v>-37.5</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-13.636363636363</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F24" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.911392405063</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="I24" s="14">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="J24" s="14">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="K24" s="15">
-        <v>-38.483965014577</v>
+        <v>-37.005649717514</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.267912772585</v>
+        <v>-34.218289085545</v>
       </c>
       <c r="M24" s="15">
-        <v>-19.465648854961</v>
+        <v>-21.478873239436</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>4</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-43.75</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="I25" s="14">
         <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K25" s="15">
-        <v>-26.153846153846</v>
+        <v>-28.358208955223</v>
       </c>
       <c r="L25" s="15">
-        <v>-36</v>
+        <v>-41.463414634146</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>9</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-57.142857142857</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-42.222222222222</v>
+        <v>-31.707317073170</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="J26" s="14">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K26" s="15">
-        <v>-25.925925925925</v>
+        <v>-22.695035460992</v>
       </c>
       <c r="L26" s="15">
-        <v>-25.373134328358</v>
+        <v>-22.142857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>-23.664122137404</v>
+        <v>-22.142857142857</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>2</v>
@@ -1403,16 +1403,16 @@
         <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="L27" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>150</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
         <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>21.052631578947</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,10 +1558,10 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
         <v>100</v>

--- a/data/source/weekly/cs-en-us-066pct.xlsx
+++ b/data/source/weekly/cs-en-us-066pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,20 +895,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -920,13 +920,13 @@
         <v>75</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M15" s="15">
         <v>250</v>
       </c>
       <c r="N15" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
         <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.405405405405</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.894736842105</v>
+        <v>2.564102564102</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.677966101694</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.220472440944</v>
+        <v>-85.130111524163</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-75</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>9.523809523809</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.049382716049</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M17" s="15">
-        <v>61.904761904761</v>
+        <v>46.938775510204</v>
       </c>
       <c r="N17" s="15">
-        <v>-32</v>
+        <v>-35.135135135135</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>400</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>83.333333333333</v>
+        <v>120</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-9.302325581395</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.878048780487</v>
+        <v>2.439024390243</v>
       </c>
       <c r="M18" s="15">
-        <v>-70.229007633587</v>
+        <v>-69.117647058823</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.298969072165</v>
+        <v>-93.069306930693</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.363636363636</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="I19" s="14">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.981132075471</v>
+        <v>-17.441860465116</v>
       </c>
       <c r="L19" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.067961165048</v>
       </c>
       <c r="M19" s="15">
-        <v>1.538461538461</v>
+        <v>5.185185185185</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.608695652173</v>
+        <v>-40.833333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-62.5</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="I20" s="14">
         <v>83</v>
       </c>
       <c r="J20" s="14">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K20" s="15">
-        <v>3.75</v>
+        <v>-4.597701149425</v>
       </c>
       <c r="L20" s="15">
-        <v>45.614035087719</v>
+        <v>36.065573770491</v>
       </c>
       <c r="M20" s="15">
-        <v>66</v>
+        <v>56.603773584905</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.556221889055</v>
+        <v>-88.260254596888</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.256880733944</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I21" s="17">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="J21" s="17">
-        <v>391</v>
+        <v>426</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.649616368286</v>
+        <v>-9.154929577464</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.915094339622</v>
+        <v>-12.244897959183</v>
       </c>
       <c r="M21" s="18">
-        <v>-11.835748792270</v>
+        <v>-12.045454545454</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.195333695062</v>
+        <v>-80.102827763496</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>18.181818181818</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F24" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G24" s="14">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.084507042253</v>
+        <v>7.575757575757</v>
       </c>
       <c r="I24" s="14">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="J24" s="14">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="K24" s="15">
-        <v>-37.005649717514</v>
+        <v>-36.170212765957</v>
       </c>
       <c r="L24" s="15">
-        <v>-34.218289085545</v>
+        <v>-32.773109243697</v>
       </c>
       <c r="M24" s="15">
-        <v>-21.478873239436</v>
+        <v>-22.077922077922</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>-58.823529411764</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J25" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K25" s="15">
-        <v>-28.358208955223</v>
+        <v>-26.470588235294</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.463414634146</v>
+        <v>-43.181818181818</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1353,28 +1353,28 @@
         <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-31.707317073170</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I26" s="14">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>-22.695035460992</v>
+        <v>-19.727891156462</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.142857142857</v>
+        <v>-16.312056737588</v>
       </c>
       <c r="M26" s="15">
-        <v>-22.142857142857</v>
+        <v>-22.875816993464</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>11</v>
@@ -1412,7 +1412,7 @@
         <v>120</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>7</v>
-      </c>
-      <c r="G28" s="14">
-        <v>3</v>
-      </c>
       <c r="H28" s="15">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I28" s="14">
         <v>24</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1500,15 +1500,15 @@
         <v>200</v>
       </c>
       <c r="N29" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1541,15 +1541,15 @@
         <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,25 +1558,25 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J31" s="14">
         <v>5</v>
       </c>
       <c r="K31" s="15">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L31" s="15">
-        <v>50</v>
+        <v>83.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
